--- a/artfynd/A 32865-2024 artfynd.xlsx
+++ b/artfynd/A 32865-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,1658 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128469414</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91378</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Mattismyren, Mattismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>395670</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7047399</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Löv-och örtrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128469307</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92295</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mattismyren, Mattismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>395695</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7047399</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Löv-och örtrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128469095</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80136</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mattismyren, Mattismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>395885</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7047425</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Löv-och örtrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128471532</v>
+      </c>
+      <c r="B6" t="n">
+        <v>86888</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3624</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Strimspindling</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mattismyren, Mattismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>396279</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7047043</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Ca 40-årig granskog på frisk mark. Äldre skog angränsar.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128469755</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92057</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mattismyren, Mattismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>395860</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7046762</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Luckig, lågproduktiv grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128469015</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80136</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mattismyren, Mattismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>395929</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7047425</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Löv-och örtrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128469040</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mattismyren, Mattismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>395897</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7047432</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Löv-och örtrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128469305</v>
+      </c>
+      <c r="B10" t="n">
+        <v>88617</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4405</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Diskvaxskivling</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hygrophorus discoideus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Pers.) Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mattismyren, Mattismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>395695</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7047399</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Löv-och örtrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128469271</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78015</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mattismyren, Mattismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>395712</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7047420</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Löv-och örtrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128469090</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mattismyren, Mattismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>395885</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7047425</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Löv-och örtrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128469753</v>
+      </c>
+      <c r="B13" t="n">
+        <v>88761</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>510</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mattismyren, Mattismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>395860</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7046762</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Luckig, lågproduktiv grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128469788</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91378</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Mattismyren, Mattismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>395963</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7046819</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Frodig svacka i grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128471036</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79191</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Mattismyren, Mattismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>396213</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7046988</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Brant grannaturskog ner mot en å</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128471195</v>
+      </c>
+      <c r="B16" t="n">
+        <v>89410</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>275</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kejsarskivling</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Catathelasma imperiale</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Singer</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Mattismyren, Mattismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>396278</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7047041</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Ca 40-årig granskog på frisk mark. Äldre skog angränsar.</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128469302</v>
+      </c>
+      <c r="B17" t="n">
+        <v>95710</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mattismyren, Mattismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>395696</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7047406</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Löv-och örtrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128469044</v>
+      </c>
+      <c r="B18" t="n">
+        <v>75156</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mattismyren, Mattismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>395897</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7047432</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Löv-och örtrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32865-2024 artfynd.xlsx
+++ b/artfynd/A 32865-2024 artfynd.xlsx
@@ -991,45 +991,44 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128469095</v>
+        <v>128471532</v>
       </c>
       <c r="B5" t="n">
-        <v>80136</v>
+        <v>86888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>3624</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mattismyren, Mattismyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>395885</v>
+        <v>396279</v>
       </c>
       <c r="R5" t="n">
-        <v>7047425</v>
+        <v>7047043</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,12 +1069,13 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Löv-och örtrik grannaturskog</t>
+          <t>Ca 40-årig granskog på frisk mark. Äldre skog angränsar.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1093,44 +1093,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128471532</v>
+        <v>128469095</v>
       </c>
       <c r="B6" t="n">
-        <v>86888</v>
+        <v>80136</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3624</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mattismyren, Mattismyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>396279</v>
+        <v>395885</v>
       </c>
       <c r="R6" t="n">
-        <v>7047043</v>
+        <v>7047425</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1171,13 +1172,12 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Ca 40-årig granskog på frisk mark. Äldre skog angränsar.</t>
+          <t>Löv-och örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1195,48 +1195,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128469755</v>
+        <v>128469040</v>
       </c>
       <c r="B7" t="n">
-        <v>92057</v>
+        <v>79032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mattismyren, Mattismyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>395860</v>
+        <v>395897</v>
       </c>
       <c r="R7" t="n">
-        <v>7046762</v>
+        <v>7047432</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,13 +1274,12 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Luckig, lågproduktiv grannaturskog</t>
+          <t>Löv-och örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1403,45 +1399,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128469040</v>
+        <v>128469755</v>
       </c>
       <c r="B9" t="n">
-        <v>79032</v>
+        <v>92057</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mattismyren, Mattismyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>395897</v>
+        <v>395860</v>
       </c>
       <c r="R9" t="n">
-        <v>7047432</v>
+        <v>7046762</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1482,12 +1481,13 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Löv-och örtrik grannaturskog</t>
+          <t>Luckig, lågproduktiv grannaturskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128471036</v>
+        <v>128471195</v>
       </c>
       <c r="B15" t="n">
-        <v>79191</v>
+        <v>89410</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2034,21 +2034,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1249</v>
+        <v>275</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kejsarskivling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Catathelasma imperiale</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(P.Karst.) Singer</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>396213</v>
+        <v>396278</v>
       </c>
       <c r="R15" t="n">
-        <v>7046988</v>
+        <v>7047041</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Brant grannaturskog ner mot en å</t>
+          <t>Ca 40-årig granskog på frisk mark. Äldre skog angränsar.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2129,48 +2129,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128471195</v>
+        <v>128469044</v>
       </c>
       <c r="B16" t="n">
-        <v>89410</v>
+        <v>75156</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>275</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kejsarskivling</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Catathelasma imperiale</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Singer</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mattismyren, Mattismyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>396278</v>
+        <v>395897</v>
       </c>
       <c r="R16" t="n">
-        <v>7047041</v>
+        <v>7047432</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2211,13 +2208,12 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Ca 40-årig granskog på frisk mark. Äldre skog angränsar.</t>
+          <t>Löv-och örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2235,45 +2231,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128469302</v>
+        <v>128471036</v>
       </c>
       <c r="B17" t="n">
-        <v>95710</v>
+        <v>79191</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2809</v>
+        <v>1249</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Mattismyren, Mattismyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>395696</v>
+        <v>396213</v>
       </c>
       <c r="R17" t="n">
-        <v>7047406</v>
+        <v>7046988</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2314,12 +2313,13 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Löv-och örtrik grannaturskog</t>
+          <t>Brant grannaturskog ner mot en å</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2337,32 +2337,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128469044</v>
+        <v>128469302</v>
       </c>
       <c r="B18" t="n">
-        <v>75156</v>
+        <v>95710</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>2809</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>395897</v>
+        <v>395696</v>
       </c>
       <c r="R18" t="n">
-        <v>7047432</v>
+        <v>7047406</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 32865-2024 artfynd.xlsx
+++ b/artfynd/A 32865-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>128469414</v>
       </c>
       <c r="B3" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128469307</v>
       </c>
       <c r="B4" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128471532</v>
       </c>
       <c r="B5" t="n">
-        <v>86888</v>
+        <v>86980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128469095</v>
       </c>
       <c r="B6" t="n">
-        <v>80136</v>
+        <v>80189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>128469040</v>
       </c>
       <c r="B7" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>128469015</v>
       </c>
       <c r="B8" t="n">
-        <v>80136</v>
+        <v>80189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>128469755</v>
       </c>
       <c r="B9" t="n">
-        <v>92057</v>
+        <v>92149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>128469305</v>
       </c>
       <c r="B10" t="n">
-        <v>88617</v>
+        <v>88709</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>128469271</v>
       </c>
       <c r="B11" t="n">
-        <v>78015</v>
+        <v>78060</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>128469090</v>
       </c>
       <c r="B12" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>128469753</v>
       </c>
       <c r="B13" t="n">
-        <v>88761</v>
+        <v>88853</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>128469788</v>
       </c>
       <c r="B14" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>128471195</v>
       </c>
       <c r="B15" t="n">
-        <v>89410</v>
+        <v>89502</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>128469044</v>
       </c>
       <c r="B16" t="n">
-        <v>75156</v>
+        <v>75171</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>128471036</v>
       </c>
       <c r="B17" t="n">
-        <v>79191</v>
+        <v>79242</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>128469302</v>
       </c>
       <c r="B18" t="n">
-        <v>95710</v>
+        <v>95803</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 32865-2024 artfynd.xlsx
+++ b/artfynd/A 32865-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>128469414</v>
       </c>
       <c r="B3" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128469307</v>
       </c>
       <c r="B4" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128471532</v>
       </c>
       <c r="B5" t="n">
-        <v>86980</v>
+        <v>86985</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128469095</v>
       </c>
       <c r="B6" t="n">
-        <v>80189</v>
+        <v>80193</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>128469040</v>
       </c>
       <c r="B7" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>128469015</v>
       </c>
       <c r="B8" t="n">
-        <v>80189</v>
+        <v>80193</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>128469755</v>
       </c>
       <c r="B9" t="n">
-        <v>92149</v>
+        <v>92155</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>128469305</v>
       </c>
       <c r="B10" t="n">
-        <v>88709</v>
+        <v>88715</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>128469271</v>
       </c>
       <c r="B11" t="n">
-        <v>78060</v>
+        <v>78064</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>128469090</v>
       </c>
       <c r="B12" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>128469753</v>
       </c>
       <c r="B13" t="n">
-        <v>88853</v>
+        <v>88859</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>128469788</v>
       </c>
       <c r="B14" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>128471195</v>
       </c>
       <c r="B15" t="n">
-        <v>89502</v>
+        <v>89508</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>128469044</v>
       </c>
       <c r="B16" t="n">
-        <v>75171</v>
+        <v>75175</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>128471036</v>
       </c>
       <c r="B17" t="n">
-        <v>79242</v>
+        <v>79246</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>128469302</v>
       </c>
       <c r="B18" t="n">
-        <v>95803</v>
+        <v>95809</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 32865-2024 artfynd.xlsx
+++ b/artfynd/A 32865-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>128469414</v>
       </c>
       <c r="B3" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128469307</v>
       </c>
       <c r="B4" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128471532</v>
       </c>
       <c r="B5" t="n">
-        <v>86985</v>
+        <v>86991</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>128469755</v>
       </c>
       <c r="B9" t="n">
-        <v>92155</v>
+        <v>92161</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>128469305</v>
       </c>
       <c r="B10" t="n">
-        <v>88715</v>
+        <v>88721</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>128469753</v>
       </c>
       <c r="B13" t="n">
-        <v>88859</v>
+        <v>88865</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>128469788</v>
       </c>
       <c r="B14" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>128471195</v>
       </c>
       <c r="B15" t="n">
-        <v>89508</v>
+        <v>89514</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>128469302</v>
       </c>
       <c r="B18" t="n">
-        <v>95809</v>
+        <v>95815</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 32865-2024 artfynd.xlsx
+++ b/artfynd/A 32865-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>128469414</v>
       </c>
       <c r="B3" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128469307</v>
       </c>
       <c r="B4" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128471532</v>
       </c>
       <c r="B5" t="n">
-        <v>86991</v>
+        <v>86993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128469095</v>
       </c>
       <c r="B6" t="n">
-        <v>80193</v>
+        <v>80195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>128469040</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>128469015</v>
       </c>
       <c r="B8" t="n">
-        <v>80193</v>
+        <v>80195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>128469755</v>
       </c>
       <c r="B9" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>128469305</v>
       </c>
       <c r="B10" t="n">
-        <v>88721</v>
+        <v>88723</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>128469271</v>
       </c>
       <c r="B11" t="n">
-        <v>78064</v>
+        <v>78066</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>128469090</v>
       </c>
       <c r="B12" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>128469753</v>
       </c>
       <c r="B13" t="n">
-        <v>88865</v>
+        <v>88867</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>128469788</v>
       </c>
       <c r="B14" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>128471195</v>
       </c>
       <c r="B15" t="n">
-        <v>89514</v>
+        <v>89516</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>128469044</v>
       </c>
       <c r="B16" t="n">
-        <v>75175</v>
+        <v>75177</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>128471036</v>
       </c>
       <c r="B17" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>128469302</v>
       </c>
       <c r="B18" t="n">
-        <v>95815</v>
+        <v>95817</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 32865-2024 artfynd.xlsx
+++ b/artfynd/A 32865-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>128469414</v>
       </c>
       <c r="B3" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128469307</v>
       </c>
       <c r="B4" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>128469755</v>
       </c>
       <c r="B9" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>128469788</v>
       </c>
       <c r="B14" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>128469302</v>
       </c>
       <c r="B18" t="n">
-        <v>95817</v>
+        <v>95818</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 32865-2024 artfynd.xlsx
+++ b/artfynd/A 32865-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>128469414</v>
       </c>
       <c r="B3" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128469307</v>
       </c>
       <c r="B4" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128471532</v>
       </c>
       <c r="B5" t="n">
-        <v>86993</v>
+        <v>87020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128469095</v>
       </c>
       <c r="B6" t="n">
-        <v>80195</v>
+        <v>80222</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>128469040</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>128469015</v>
       </c>
       <c r="B8" t="n">
-        <v>80195</v>
+        <v>80222</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>128469755</v>
       </c>
       <c r="B9" t="n">
-        <v>92164</v>
+        <v>92191</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>128469305</v>
       </c>
       <c r="B10" t="n">
-        <v>88723</v>
+        <v>88750</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>128469271</v>
       </c>
       <c r="B11" t="n">
-        <v>78066</v>
+        <v>78093</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>128469090</v>
       </c>
       <c r="B12" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>128469753</v>
       </c>
       <c r="B13" t="n">
-        <v>88867</v>
+        <v>88894</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>128469788</v>
       </c>
       <c r="B14" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>128471195</v>
       </c>
       <c r="B15" t="n">
-        <v>89516</v>
+        <v>89543</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>128469044</v>
       </c>
       <c r="B16" t="n">
-        <v>75177</v>
+        <v>75204</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>128471036</v>
       </c>
       <c r="B17" t="n">
-        <v>79248</v>
+        <v>79275</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>128469302</v>
       </c>
       <c r="B18" t="n">
-        <v>95818</v>
+        <v>95845</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 32865-2024 artfynd.xlsx
+++ b/artfynd/A 32865-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>128469414</v>
       </c>
       <c r="B3" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128469307</v>
       </c>
       <c r="B4" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128471532</v>
       </c>
       <c r="B5" t="n">
-        <v>87020</v>
+        <v>87024</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128469095</v>
       </c>
       <c r="B6" t="n">
-        <v>80222</v>
+        <v>80226</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>128469040</v>
       </c>
       <c r="B7" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>128469015</v>
       </c>
       <c r="B8" t="n">
-        <v>80222</v>
+        <v>80226</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>128469755</v>
       </c>
       <c r="B9" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>128469305</v>
       </c>
       <c r="B10" t="n">
-        <v>88750</v>
+        <v>88754</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>128469271</v>
       </c>
       <c r="B11" t="n">
-        <v>78093</v>
+        <v>78097</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>128469090</v>
       </c>
       <c r="B12" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>128469753</v>
       </c>
       <c r="B13" t="n">
-        <v>88894</v>
+        <v>88899</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>128469788</v>
       </c>
       <c r="B14" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>128471195</v>
       </c>
       <c r="B15" t="n">
-        <v>89543</v>
+        <v>89548</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>128469044</v>
       </c>
       <c r="B16" t="n">
-        <v>75204</v>
+        <v>75205</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>128471036</v>
       </c>
       <c r="B17" t="n">
-        <v>79275</v>
+        <v>79279</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>128469302</v>
       </c>
       <c r="B18" t="n">
-        <v>95845</v>
+        <v>95851</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 32865-2024 artfynd.xlsx
+++ b/artfynd/A 32865-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>128469414</v>
       </c>
       <c r="B3" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128469307</v>
       </c>
       <c r="B4" t="n">
-        <v>92434</v>
+        <v>92439</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128471532</v>
       </c>
       <c r="B5" t="n">
-        <v>87024</v>
+        <v>87025</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>128469755</v>
       </c>
       <c r="B9" t="n">
-        <v>92196</v>
+        <v>92201</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>128469305</v>
       </c>
       <c r="B10" t="n">
-        <v>88754</v>
+        <v>88755</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>128469753</v>
       </c>
       <c r="B13" t="n">
-        <v>88899</v>
+        <v>88904</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>128469788</v>
       </c>
       <c r="B14" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>128471195</v>
       </c>
       <c r="B15" t="n">
-        <v>89548</v>
+        <v>89553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>128469302</v>
       </c>
       <c r="B18" t="n">
-        <v>95851</v>
+        <v>95858</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 32865-2024 artfynd.xlsx
+++ b/artfynd/A 32865-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>128469414</v>
       </c>
       <c r="B3" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128469307</v>
       </c>
       <c r="B4" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128471532</v>
       </c>
       <c r="B5" t="n">
-        <v>87025</v>
+        <v>87029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128469095</v>
       </c>
       <c r="B6" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>128469040</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>128469015</v>
       </c>
       <c r="B8" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>128469755</v>
       </c>
       <c r="B9" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>128469305</v>
       </c>
       <c r="B10" t="n">
-        <v>88755</v>
+        <v>88759</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>128469271</v>
       </c>
       <c r="B11" t="n">
-        <v>78097</v>
+        <v>78101</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>128469090</v>
       </c>
       <c r="B12" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>128469753</v>
       </c>
       <c r="B13" t="n">
-        <v>88904</v>
+        <v>88908</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>128469788</v>
       </c>
       <c r="B14" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>128471195</v>
       </c>
       <c r="B15" t="n">
-        <v>89553</v>
+        <v>89557</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>128469044</v>
       </c>
       <c r="B16" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>128471036</v>
       </c>
       <c r="B17" t="n">
-        <v>79279</v>
+        <v>79283</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>128469302</v>
       </c>
       <c r="B18" t="n">
-        <v>95858</v>
+        <v>95862</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 32865-2024 artfynd.xlsx
+++ b/artfynd/A 32865-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>128469414</v>
       </c>
       <c r="B3" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128469307</v>
       </c>
       <c r="B4" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128471532</v>
       </c>
       <c r="B5" t="n">
-        <v>87029</v>
+        <v>87034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128469095</v>
       </c>
       <c r="B6" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>128469040</v>
       </c>
       <c r="B7" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>128469015</v>
       </c>
       <c r="B8" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>128469755</v>
       </c>
       <c r="B9" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>128469305</v>
       </c>
       <c r="B10" t="n">
-        <v>88759</v>
+        <v>88764</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>128469271</v>
       </c>
       <c r="B11" t="n">
-        <v>78101</v>
+        <v>78042</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>128469090</v>
       </c>
       <c r="B12" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>128469753</v>
       </c>
       <c r="B13" t="n">
-        <v>88908</v>
+        <v>88913</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>128469788</v>
       </c>
       <c r="B14" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>128471195</v>
       </c>
       <c r="B15" t="n">
-        <v>89557</v>
+        <v>89562</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>128469044</v>
       </c>
       <c r="B16" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>128471036</v>
       </c>
       <c r="B17" t="n">
-        <v>79283</v>
+        <v>79188</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>128469302</v>
       </c>
       <c r="B18" t="n">
-        <v>95862</v>
+        <v>95869</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 32865-2024 artfynd.xlsx
+++ b/artfynd/A 32865-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111929309</v>
+        <v>128471195</v>
       </c>
       <c r="B2" t="n">
-        <v>56753</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>90006</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>275</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kejsarskivling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Catathelasma imperiale</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Daltjärnen, Jmt</t>
+          <t>Mattismyren, Mattismyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>395438</v>
+        <v>396278</v>
       </c>
       <c r="R2" t="n">
-        <v>7047062</v>
+        <v>7047041</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,17 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-12</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,28 +757,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Ca 35-årig granskog på frisk mark. Äldre skog angränsar.</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128469414</v>
+        <v>128469753</v>
       </c>
       <c r="B3" t="n">
-        <v>91533</v>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,34 +792,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mattismyren, Mattismyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>395670</v>
+        <v>395860</v>
       </c>
       <c r="R3" t="n">
-        <v>7047399</v>
+        <v>7046762</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,12 +863,13 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Löv-och örtrik grannaturskog</t>
+          <t>Luckig, lågproduktiv grannaturskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -889,45 +887,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128469307</v>
+        <v>128471036</v>
       </c>
       <c r="B4" t="n">
-        <v>92451</v>
+        <v>79486</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>1249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Mattismyren, Mattismyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>395695</v>
+        <v>396213</v>
       </c>
       <c r="R4" t="n">
-        <v>7047399</v>
+        <v>7046988</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,12 +969,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Löv-och örtrik grannaturskog</t>
+          <t>Brant grannaturskog ner mot en å</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -991,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128471532</v>
+        <v>128469755</v>
       </c>
       <c r="B5" t="n">
-        <v>87394</v>
+        <v>92632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,19 +1004,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3624</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -1025,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>396279</v>
+        <v>395860</v>
       </c>
       <c r="R5" t="n">
-        <v>7047043</v>
+        <v>7046762</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,7 +1081,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Ca 35-årig granskog på frisk mark. Äldre skog angränsar.</t>
+          <t>Luckig, lågproduktiv grannaturskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1093,45 +1099,44 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128469095</v>
+        <v>128471532</v>
       </c>
       <c r="B6" t="n">
-        <v>80135</v>
+        <v>87474</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>3624</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mattismyren, Mattismyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>395885</v>
+        <v>396279</v>
       </c>
       <c r="R6" t="n">
-        <v>7047425</v>
+        <v>7047043</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,12 +1177,13 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Löv-och örtrik grannaturskog</t>
+          <t>Ca 35-årig granskog på frisk mark. Äldre skog angränsar.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1195,10 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128469040</v>
+        <v>111929309</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,37 +1212,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mattismyren, Mattismyren, Jmt</t>
+          <t>Daltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>395897</v>
+        <v>395438</v>
       </c>
       <c r="R7" t="n">
-        <v>7047432</v>
+        <v>7047062</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1260,12 +1271,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2023-07-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2023-07-12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1276,21 +1292,16 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Löv-och örtrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1300,7 +1311,7 @@
         <v>128469015</v>
       </c>
       <c r="B8" t="n">
-        <v>80135</v>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1399,48 +1410,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128469755</v>
+        <v>128469095</v>
       </c>
       <c r="B9" t="n">
-        <v>92213</v>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mattismyren, Mattismyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>395860</v>
+        <v>395885</v>
       </c>
       <c r="R9" t="n">
-        <v>7046762</v>
+        <v>7047425</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,13 +1489,12 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Luckig, lågproduktiv grannaturskog</t>
+          <t>Löv-och örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1505,10 +1512,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128469305</v>
+        <v>128469302</v>
       </c>
       <c r="B10" t="n">
-        <v>88766</v>
+        <v>96338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,21 +1523,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4405</v>
+        <v>2809</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1547,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>395695</v>
+        <v>395696</v>
       </c>
       <c r="R10" t="n">
-        <v>7047399</v>
+        <v>7047406</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,32 +1614,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128469271</v>
+        <v>128469305</v>
       </c>
       <c r="B11" t="n">
-        <v>78042</v>
+        <v>89143</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228579</v>
+        <v>4405</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,10 +1649,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>395712</v>
+        <v>395695</v>
       </c>
       <c r="R11" t="n">
-        <v>7047420</v>
+        <v>7047399</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,32 +1716,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128469090</v>
+        <v>128469307</v>
       </c>
       <c r="B12" t="n">
-        <v>80134</v>
+        <v>92869</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1751,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>395885</v>
+        <v>395695</v>
       </c>
       <c r="R12" t="n">
-        <v>7047425</v>
+        <v>7047399</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,48 +1818,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128469753</v>
+        <v>128469040</v>
       </c>
       <c r="B13" t="n">
-        <v>88915</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mattismyren, Mattismyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>395860</v>
+        <v>395897</v>
       </c>
       <c r="R13" t="n">
-        <v>7046762</v>
+        <v>7047432</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1893,13 +1897,12 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Luckig, lågproduktiv grannaturskog</t>
+          <t>Löv-och örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1917,10 +1920,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128469788</v>
+        <v>128469044</v>
       </c>
       <c r="B14" t="n">
-        <v>91533</v>
+        <v>83307</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1928,37 +1931,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Mattismyren, Mattismyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>395963</v>
+        <v>395897</v>
       </c>
       <c r="R14" t="n">
-        <v>7046819</v>
+        <v>7047432</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1999,13 +1999,12 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Frodig svacka i grannaturskog</t>
+          <t>Löv-och örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2023,48 +2022,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128471195</v>
+        <v>128469090</v>
       </c>
       <c r="B15" t="n">
-        <v>89923</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>275</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kejsarskivling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Catathelasma imperiale</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Mattismyren, Mattismyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>396278</v>
+        <v>395885</v>
       </c>
       <c r="R15" t="n">
-        <v>7047041</v>
+        <v>7047425</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2105,13 +2101,12 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Ca 35-årig granskog på frisk mark. Äldre skog angränsar.</t>
+          <t>Löv-och örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2129,10 +2124,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128469044</v>
+        <v>128469271</v>
       </c>
       <c r="B16" t="n">
-        <v>83005</v>
+        <v>78339</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2140,21 +2135,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2164,10 +2159,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>395897</v>
+        <v>395712</v>
       </c>
       <c r="R16" t="n">
-        <v>7047432</v>
+        <v>7047420</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2228,214 +2223,6 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>128471036</v>
-      </c>
-      <c r="B17" t="n">
-        <v>79188</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>1249</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Norsk näverlav</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Platismatia norvegica</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Mattismyren, Mattismyren, Jmt</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>396213</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7046988</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2025-09-15</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2025-09-15</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Brant grannaturskog ner mot en å</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>128469302</v>
-      </c>
-      <c r="B18" t="n">
-        <v>95872</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>2809</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Mörk husmossa</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Hylocomiastrum umbratum</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Mattismyren, Mattismyren, Jmt</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>395696</v>
-      </c>
-      <c r="R18" t="n">
-        <v>7047406</v>
-      </c>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2025-09-15</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2025-09-15</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Löv-och örtrik grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32865-2024 artfynd.xlsx
+++ b/artfynd/A 32865-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128471195</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128469753</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128471036</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128469015</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1194,6 +1219,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128469095</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1296,6 +1326,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128469302</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1402,6 +1437,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128469755</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1504,6 +1544,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128471532</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1606,6 +1651,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128469305</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1708,6 +1758,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128469307</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1810,6 +1865,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128469040</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1912,6 +1972,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128469044</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2014,6 +2079,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128469090</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2121,6 +2191,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111929309</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2223,8 +2298,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128469271</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>